--- a/ValueSet-location-type-vs.xlsx
+++ b/ValueSet-location-type-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T10:31:38+00:00</t>
+    <t>2025-05-30T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-location-type-vs.xlsx
+++ b/ValueSet-location-type-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T11:48:20+00:00</t>
+    <t>2025-05-30T11:53:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-location-type-vs.xlsx
+++ b/ValueSet-location-type-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T11:53:21+00:00</t>
+    <t>2025-05-30T12:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
